--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,304 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121430727</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98001</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ensta, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637924</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6554984</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121430728</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98001</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ensta, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>637926</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6554988</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121430367</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108704</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ensta, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>637969</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B5" t="n">
-        <v>98001</v>
+        <v>108704</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,23 +1027,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R5" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1211,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B7" t="n">
-        <v>108704</v>
+        <v>98001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,27 +1227,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R7" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B5" t="n">
-        <v>108704</v>
+        <v>98014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,27 +1027,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R5" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,7 +1116,7 @@
         <v>121430728</v>
       </c>
       <c r="B6" t="n">
-        <v>98001</v>
+        <v>98014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B7" t="n">
-        <v>98001</v>
+        <v>108717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,23 +1223,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R7" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430727</v>
+        <v>121430728</v>
       </c>
       <c r="B5" t="n">
-        <v>98014</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637924</v>
+        <v>637926</v>
       </c>
       <c r="R5" t="n">
-        <v>6554984</v>
+        <v>6554988</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430728</v>
+        <v>121430727</v>
       </c>
       <c r="B6" t="n">
-        <v>98014</v>
+        <v>98015</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637926</v>
+        <v>637924</v>
       </c>
       <c r="R6" t="n">
-        <v>6554988</v>
+        <v>6554984</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,7 +1214,7 @@
         <v>121430367</v>
       </c>
       <c r="B7" t="n">
-        <v>108717</v>
+        <v>108718</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430728</v>
+        <v>121430367</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>108721</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,23 +1027,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637926</v>
+        <v>637969</v>
       </c>
       <c r="R5" t="n">
-        <v>6554988</v>
+        <v>6555000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1120,7 @@
         <v>121430727</v>
       </c>
       <c r="B6" t="n">
-        <v>98015</v>
+        <v>98018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430367</v>
+        <v>121430728</v>
       </c>
       <c r="B7" t="n">
-        <v>108718</v>
+        <v>98018</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,27 +1227,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637969</v>
+        <v>637926</v>
       </c>
       <c r="R7" t="n">
-        <v>6555000</v>
+        <v>6554988</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430367</v>
+        <v>121430728</v>
       </c>
       <c r="B5" t="n">
-        <v>108721</v>
+        <v>98018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,27 +1027,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637969</v>
+        <v>637926</v>
       </c>
       <c r="R5" t="n">
-        <v>6555000</v>
+        <v>6554988</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B6" t="n">
-        <v>98018</v>
+        <v>108721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,23 +1125,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R6" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430728</v>
+        <v>121430727</v>
       </c>
       <c r="B7" t="n">
         <v>98018</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637926</v>
+        <v>637924</v>
       </c>
       <c r="R7" t="n">
-        <v>6554988</v>
+        <v>6554984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430728</v>
+        <v>121430367</v>
       </c>
       <c r="B5" t="n">
-        <v>98018</v>
+        <v>108727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,23 +1027,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637926</v>
+        <v>637969</v>
       </c>
       <c r="R5" t="n">
-        <v>6554988</v>
+        <v>6555000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B6" t="n">
-        <v>108721</v>
+        <v>98024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,27 +1129,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R6" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430727</v>
+        <v>121430728</v>
       </c>
       <c r="B7" t="n">
-        <v>98018</v>
+        <v>98024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637924</v>
+        <v>637926</v>
       </c>
       <c r="R7" t="n">
-        <v>6554984</v>
+        <v>6554988</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B5" t="n">
-        <v>108727</v>
+        <v>98025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,27 +1027,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R5" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B6" t="n">
-        <v>98024</v>
+        <v>108728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,23 +1125,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R6" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
         <v>121430728</v>
       </c>
       <c r="B7" t="n">
-        <v>98024</v>
+        <v>98025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430367</v>
+        <v>121430728</v>
       </c>
       <c r="B6" t="n">
-        <v>108728</v>
+        <v>98025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,27 +1125,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637969</v>
+        <v>637926</v>
       </c>
       <c r="R6" t="n">
-        <v>6555000</v>
+        <v>6554988</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430728</v>
+        <v>121430367</v>
       </c>
       <c r="B7" t="n">
-        <v>98025</v>
+        <v>108728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,23 +1223,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637926</v>
+        <v>637969</v>
       </c>
       <c r="R7" t="n">
-        <v>6554988</v>
+        <v>6555000</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B5" t="n">
-        <v>98025</v>
+        <v>108728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,23 +1027,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R5" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1211,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B7" t="n">
-        <v>108728</v>
+        <v>98025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,27 +1227,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R7" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B5" t="n">
-        <v>108728</v>
+        <v>98025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,27 +1027,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R5" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430728</v>
+        <v>121430367</v>
       </c>
       <c r="B6" t="n">
-        <v>98025</v>
+        <v>108728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,23 +1125,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637926</v>
+        <v>637969</v>
       </c>
       <c r="R6" t="n">
-        <v>6554988</v>
+        <v>6555000</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430727</v>
+        <v>121430728</v>
       </c>
       <c r="B7" t="n">
         <v>98025</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637924</v>
+        <v>637926</v>
       </c>
       <c r="R7" t="n">
-        <v>6554984</v>
+        <v>6554988</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B5" t="n">
-        <v>98025</v>
+        <v>108736</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,23 +1027,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R5" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430367</v>
+        <v>121430728</v>
       </c>
       <c r="B6" t="n">
-        <v>108728</v>
+        <v>98033</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,27 +1129,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637969</v>
+        <v>637926</v>
       </c>
       <c r="R6" t="n">
-        <v>6555000</v>
+        <v>6554988</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430728</v>
+        <v>121430727</v>
       </c>
       <c r="B7" t="n">
-        <v>98025</v>
+        <v>98033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637926</v>
+        <v>637924</v>
       </c>
       <c r="R7" t="n">
-        <v>6554988</v>
+        <v>6554984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430367</v>
+        <v>121430728</v>
       </c>
       <c r="B5" t="n">
-        <v>108736</v>
+        <v>98033</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,27 +1027,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637969</v>
+        <v>637926</v>
       </c>
       <c r="R5" t="n">
-        <v>6555000</v>
+        <v>6554988</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430727</v>
+        <v>121430367</v>
       </c>
       <c r="B6" t="n">
-        <v>98033</v>
+        <v>108736</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,23 +1125,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637924</v>
+        <v>637969</v>
       </c>
       <c r="R6" t="n">
-        <v>6554984</v>
+        <v>6555000</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430728</v>
+        <v>121430727</v>
       </c>
       <c r="B7" t="n">
         <v>98033</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637926</v>
+        <v>637924</v>
       </c>
       <c r="R7" t="n">
-        <v>6554988</v>
+        <v>6554984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113023973</v>
+        <v>113023952</v>
       </c>
       <c r="B2" t="n">
-        <v>97234</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637923</v>
+        <v>637969</v>
       </c>
       <c r="R2" t="n">
-        <v>6554984</v>
+        <v>6554999</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113023952</v>
+        <v>121430367</v>
       </c>
       <c r="B3" t="n">
-        <v>107886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,17 +817,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandsborg, Ensta, Srm</t>
+          <t>Ensta, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637970</v>
+        <v>637969</v>
       </c>
       <c r="R3" t="n">
-        <v>6554999</v>
+        <v>6555000</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +859,6 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,40 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif Andersson, Johan Ennerfelt</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113023974</v>
+        <v>113023973</v>
       </c>
       <c r="B4" t="n">
-        <v>97234</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637925</v>
+        <v>637923</v>
       </c>
       <c r="R4" t="n">
-        <v>6554987</v>
+        <v>6554984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430728</v>
+        <v>113023974</v>
       </c>
       <c r="B5" t="n">
-        <v>98033</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ensta, Srm</t>
+          <t>Sandsborg, Ensta, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637926</v>
+        <v>637925</v>
       </c>
       <c r="R5" t="n">
         <v>6554988</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,6 +1059,11 @@
           <t>2023-06-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1097,55 +1072,55 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Leif Andersson, Johan Ennerfelt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430367</v>
+        <v>121430727</v>
       </c>
       <c r="B6" t="n">
-        <v>108736</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637969</v>
+        <v>637924</v>
       </c>
       <c r="R6" t="n">
-        <v>6555000</v>
+        <v>6554984</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121430727</v>
+        <v>121430728</v>
       </c>
       <c r="B7" t="n">
-        <v>98033</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637924</v>
+        <v>637926</v>
       </c>
       <c r="R7" t="n">
-        <v>6554984</v>
+        <v>6554988</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 43525-2023 artfynd.xlsx
+++ b/artfynd/A 43525-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113023952</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430367</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113023973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113023974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430727</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,8 +1310,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>